--- a/таблица1 13.05.xlsx
+++ b/таблица1 13.05.xlsx
@@ -720,6 +720,422 @@
           <c:val>
             <c:numRef>
               <c:f>'Лист1'!F1:F7</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="false"/>
+    </c:legend>
+    <c:dispBlanksAs val="zero"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle>
+            <a:defPPr/>
+            <a:lvl1pPr lvl="0"/>
+            <a:lvl2pPr lvl="1"/>
+            <a:lvl3pPr lvl="2"/>
+            <a:lvl4pPr lvl="3"/>
+            <a:lvl5pPr lvl="4"/>
+            <a:lvl6pPr lvl="5"/>
+            <a:lvl7pPr lvl="6"/>
+            <a:lvl8pPr lvl="7"/>
+            <a:lvl9pPr lvl="8"/>
+          </a:lstStyle>
+          <a:p>
+            <a:r>
+              <a:t>Столбец A</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.36674007773399353"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
+    </c:title>
+    <c:autoTitleDeleted val="false"/>
+    <c:plotArea>
+      <c:pieChart>
+        <c:varyColors val="true"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>'Лист5'!A1:A7</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="false"/>
+    </c:legend>
+    <c:dispBlanksAs val="zero"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle>
+            <a:defPPr/>
+            <a:lvl1pPr lvl="0"/>
+            <a:lvl2pPr lvl="1"/>
+            <a:lvl3pPr lvl="2"/>
+            <a:lvl4pPr lvl="3"/>
+            <a:lvl5pPr lvl="4"/>
+            <a:lvl6pPr lvl="5"/>
+            <a:lvl7pPr lvl="6"/>
+            <a:lvl8pPr lvl="7"/>
+            <a:lvl9pPr lvl="8"/>
+          </a:lstStyle>
+          <a:p>
+            <a:r>
+              <a:t>Столбец B</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+    </c:title>
+    <c:autoTitleDeleted val="false"/>
+    <c:plotArea>
+      <c:pieChart>
+        <c:varyColors val="true"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>'Лист5'!B1:B7</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="false"/>
+    </c:legend>
+    <c:dispBlanksAs val="zero"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle>
+            <a:defPPr/>
+            <a:lvl1pPr lvl="0"/>
+            <a:lvl2pPr lvl="1"/>
+            <a:lvl3pPr lvl="2"/>
+            <a:lvl4pPr lvl="3"/>
+            <a:lvl5pPr lvl="4"/>
+            <a:lvl6pPr lvl="5"/>
+            <a:lvl7pPr lvl="6"/>
+            <a:lvl8pPr lvl="7"/>
+            <a:lvl9pPr lvl="8"/>
+          </a:lstStyle>
+          <a:p>
+            <a:r>
+              <a:t>Столбец C</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+    </c:title>
+    <c:autoTitleDeleted val="false"/>
+    <c:plotArea>
+      <c:pieChart>
+        <c:varyColors val="true"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="100000"/>
+                  <a:lumOff val="0"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>'Лист5'!C1:C7</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -841,6 +1257,62 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="true"/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1247775" y="2038350"/>
+    <xdr:ext cx="3978275" cy="2943225"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr hidden="false" id="7" name="Chart 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm flipH="false" flipV="false" rot="0"/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="true"/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5257799" y="2009775"/>
+    <xdr:ext cx="4140200" cy="3067050"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr hidden="false" id="8" name="Chart 8"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm flipH="false" flipV="false" rot="0"/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="true"/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9391649" y="2143124"/>
+    <xdr:ext cx="3740150" cy="2762250"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr hidden="false" id="9" name="Chart 9"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm flipH="false" flipV="false" rot="0"/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1255,6 +1727,11 @@
         <v>21</v>
       </c>
     </row>
+    <row outlineLevel="0" r="3">
+      <c r="H3" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row outlineLevel="0" r="5">
       <c r="H5" s="0" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM('Лист1'!$A$2:$B$2, 'Лист1'!E2:F2)</f>
@@ -1304,8 +1781,150 @@
   </sheetPr>
   <dimension ref="A1:Z300"/>
   <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="10.788470377394527" defaultRowHeight="15" zeroHeight="false"/>
-  <sheetData/>
+  <sheetData>
+    <row outlineLevel="0" r="1">
+      <c r="A1" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B1" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="2">
+      <c r="A2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3">
+      <c r="A3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4">
+      <c r="A4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5">
+      <c r="A5" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(A$1:A$4)</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(B$1:B$4)</f>
+        <v>4</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(C$1:C$4)</f>
+        <v>4</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(D$1:D$4)</f>
+        <v>4</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(E$1:E$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(F$1:F$4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="6">
+      <c r="A6" s="0" t="n"/>
+      <c r="B6" s="0" t="n"/>
+      <c r="C6" s="0" t="n"/>
+      <c r="D6" s="0" t="n"/>
+      <c r="E6" s="0" t="n"/>
+      <c r="F6" s="0" t="n"/>
+    </row>
+    <row outlineLevel="0" r="7">
+      <c r="A7" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(A$3:A$6)</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(B$3:B$6)</f>
+        <v>4</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(C$3:C$6)</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(D$3:D$6)</f>
+        <v>4</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(E$3:E$6)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MIN(F$3:F$6)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins bottom="0.59055554866790771" footer="0.5" header="0.5" left="0.59055554866790771" right="0.59055554866790771" top="0.59055554866790771"/>
   <pageSetup fitToHeight="0" fitToWidth="0" orientation="portrait" paperHeight="297.1798mm" paperSize="9" paperWidth="210.0438mm" scale="100"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>